--- a/templates/06_COGS_Template.xlsx
+++ b/templates/06_COGS_Template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COGS" sheetId="1" r:id="R41502a38f4a24f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COGS" sheetId="1" r:id="R7c712a8ada3b4dbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -258,16 +258,16 @@
         <x:v>Yo-Chi Albert St</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:v>25.21</x:v>
+        <x:v>24.79</x:v>
       </x:c>
       <x:c r="C2" s="7" t="n">
-        <x:v>1.7399999999999998</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="D2" s="7" t="n">
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="E2" s="7" t="n">
-        <x:v>3.1399999999999997</x:v>
+        <x:v>3.09</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -275,16 +275,16 @@
         <x:v>Yo-Chi Balaclava</x:v>
       </x:c>
       <x:c r="B3" s="7" t="n">
-        <x:v>24.2</x:v>
+        <x:v>23.830000000000002</x:v>
       </x:c>
       <x:c r="C3" s="7" t="n">
-        <x:v>1.97</x:v>
+        <x:v>1.94</x:v>
       </x:c>
       <x:c r="D3" s="7" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.41000000000000003</x:v>
       </x:c>
       <x:c r="E3" s="7" t="n">
-        <x:v>6.45</x:v>
+        <x:v>6.35</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -292,16 +292,16 @@
         <x:v>Yo-Chi Barangaroo</x:v>
       </x:c>
       <x:c r="B4" s="7" t="n">
-        <x:v>23.990000000000002</x:v>
+        <x:v>23.59</x:v>
       </x:c>
       <x:c r="C4" s="7" t="n">
-        <x:v>1.8900000000000001</x:v>
+        <x:v>1.8599999999999999</x:v>
       </x:c>
       <x:c r="D4" s="7" t="n">
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="E4" s="7" t="n">
-        <x:v>3.7800000000000002</x:v>
+        <x:v>3.7199999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -309,16 +309,16 @@
         <x:v>Yo-Chi Bondi</x:v>
       </x:c>
       <x:c r="B5" s="7" t="n">
-        <x:v>26.400000000000002</x:v>
+        <x:v>25.990000000000002</x:v>
       </x:c>
       <x:c r="C5" s="7" t="n">
-        <x:v>1.83</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="D5" s="7" t="n">
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="E5" s="7" t="n">
-        <x:v>3.9899999999999998</x:v>
+        <x:v>3.93</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -326,16 +326,16 @@
         <x:v>Yo-Chi Bondi Junction</x:v>
       </x:c>
       <x:c r="B6" s="7" t="n">
-        <x:v>25.36</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="C6" s="7" t="n">
-        <x:v>1.76</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>5.92</x:v>
+        <x:v>5.83</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -343,16 +343,16 @@
         <x:v>Yo-Chi Brighton</x:v>
       </x:c>
       <x:c r="B7" s="7" t="n">
-        <x:v>23.94</x:v>
+        <x:v>23.57</x:v>
       </x:c>
       <x:c r="C7" s="7" t="n">
-        <x:v>1.91</x:v>
+        <x:v>1.8800000000000001</x:v>
       </x:c>
       <x:c r="D7" s="7" t="n">
-        <x:v>0.41000000000000003</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>5.96</x:v>
+        <x:v>5.87</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -360,16 +360,16 @@
         <x:v>Yo-Chi Broadbeach</x:v>
       </x:c>
       <x:c r="B8" s="7" t="n">
-        <x:v>24.19</x:v>
+        <x:v>23.79</x:v>
       </x:c>
       <x:c r="C8" s="7" t="n">
-        <x:v>1.83</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="D8" s="7" t="n">
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>3.74</x:v>
+        <x:v>3.6799999999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -377,16 +377,16 @@
         <x:v>Yo-Chi Bulimba</x:v>
       </x:c>
       <x:c r="B9" s="7" t="n">
-        <x:v>26.22</x:v>
+        <x:v>25.840000000000003</x:v>
       </x:c>
       <x:c r="C9" s="7" t="n">
-        <x:v>1.73</x:v>
+        <x:v>1.7000000000000002</x:v>
       </x:c>
       <x:c r="D9" s="7" t="n">
-        <x:v>0.44999999999999996</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>5.81</x:v>
+        <x:v>5.7299999999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -394,16 +394,16 @@
         <x:v>Yo-Chi Burleigh</x:v>
       </x:c>
       <x:c r="B10" s="7" t="n">
-        <x:v>24.91</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C10" s="7" t="n">
-        <x:v>1.8599999999999999</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="D10" s="7" t="n">
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>5.1499999999999995</x:v>
+        <x:v>5.07</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -411,16 +411,16 @@
         <x:v>Yo-Chi Burwood</x:v>
       </x:c>
       <x:c r="B11" s="7" t="n">
-        <x:v>23.34</x:v>
+        <x:v>22.95</x:v>
       </x:c>
       <x:c r="C11" s="7" t="n">
-        <x:v>1.8800000000000001</x:v>
+        <x:v>1.8499999999999999</x:v>
       </x:c>
       <x:c r="D11" s="7" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>4.64</x:v>
+        <x:v>4.5600000000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -428,16 +428,16 @@
         <x:v>Yo-Chi Carlton</x:v>
       </x:c>
       <x:c r="B12" s="7" t="n">
-        <x:v>22.97</x:v>
+        <x:v>22.58</x:v>
       </x:c>
       <x:c r="C12" s="7" t="n">
-        <x:v>1.7399999999999998</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="D12" s="7" t="n">
-        <x:v>0.33999999999999997</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>4.66</x:v>
+        <x:v>4.58</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -445,16 +445,16 @@
         <x:v>Yo-Chi Castle Towers</x:v>
       </x:c>
       <x:c r="B13" s="7" t="n">
-        <x:v>24.12</x:v>
+        <x:v>23.73</x:v>
       </x:c>
       <x:c r="C13" s="7" t="n">
-        <x:v>1.9900000000000002</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="D13" s="7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.38999999999999996</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>4.38</x:v>
+        <x:v>4.31</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -462,968 +462,951 @@
         <x:v>Yo-Chi Chadstone</x:v>
       </x:c>
       <x:c r="B14" s="7" t="n">
-        <x:v>23.43</x:v>
+        <x:v>23.06</x:v>
       </x:c>
       <x:c r="C14" s="7" t="n">
-        <x:v>1.92</x:v>
+        <x:v>1.8900000000000001</x:v>
       </x:c>
       <x:c r="D14" s="7" t="n">
-        <x:v>0.33</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>6.36</x:v>
+        <x:v>6.260000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>Yo-Chi Charlestown</x:v>
+        <x:v>Yo-Chi Chatswood</x:v>
       </x:c>
       <x:c r="B15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>23.04</x:v>
       </x:c>
       <x:c r="C15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>5.38</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>Yo-Chi Chatswood</x:v>
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
       </x:c>
       <x:c r="B16" s="7" t="n">
-        <x:v>23.41</x:v>
+        <x:v>24.33</x:v>
       </x:c>
       <x:c r="C16" s="7" t="n">
-        <x:v>2.07</x:v>
+        <x:v>1.87</x:v>
       </x:c>
       <x:c r="D16" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>5.47</x:v>
+        <x:v>3.81</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+        <x:v>Yo-Chi Chippendale</x:v>
       </x:c>
       <x:c r="B17" s="7" t="n">
-        <x:v>24.73</x:v>
+        <x:v>25.47</x:v>
       </x:c>
       <x:c r="C17" s="7" t="n">
-        <x:v>1.9</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="D17" s="7" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>3.8699999999999997</x:v>
+        <x:v>6.370000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>Yo-Chi Chippendale</x:v>
+        <x:v>Yo-Chi Circular Quay</x:v>
       </x:c>
       <x:c r="B18" s="7" t="n">
-        <x:v>25.85</x:v>
+        <x:v>23.34</x:v>
       </x:c>
       <x:c r="C18" s="7" t="n">
-        <x:v>1.7000000000000002</x:v>
+        <x:v>1.82</x:v>
       </x:c>
       <x:c r="D18" s="7" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="E18" s="7" t="n">
-        <x:v>6.460000000000001</x:v>
+        <x:v>2.74</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>Yo-Chi Circular Quay</x:v>
+        <x:v>Yo-Chi Claremont</x:v>
       </x:c>
       <x:c r="B19" s="7" t="n">
-        <x:v>23.76</x:v>
+        <x:v>24.58</x:v>
       </x:c>
       <x:c r="C19" s="7" t="n">
-        <x:v>1.8499999999999999</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D19" s="7" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.35000000000000003</x:v>
       </x:c>
       <x:c r="E19" s="7" t="n">
-        <x:v>2.79</x:v>
+        <x:v>6.2</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>Yo-Chi Claremont</x:v>
+        <x:v>Yo-Chi Cockburn Central</x:v>
       </x:c>
       <x:c r="B20" s="7" t="n">
-        <x:v>24.959999999999997</x:v>
+        <x:v>23.77</x:v>
       </x:c>
       <x:c r="C20" s="7" t="n">
-        <x:v>1.52</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="D20" s="7" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>6.29</x:v>
+        <x:v>5.63</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
-        <x:v>Yo-Chi Cockburn Central</x:v>
+        <x:v>Yo-Chi Coogee</x:v>
       </x:c>
       <x:c r="B21" s="7" t="n">
-        <x:v>24.15</x:v>
+        <x:v>24.93</x:v>
       </x:c>
       <x:c r="C21" s="7" t="n">
-        <x:v>1.76</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="D21" s="7" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>5.72</x:v>
+        <x:v>4.93</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>Yo-Chi Coogee</x:v>
+        <x:v>Yo-Chi Cronulla</x:v>
       </x:c>
       <x:c r="B22" s="7" t="n">
-        <x:v>25.319999999999997</x:v>
+        <x:v>23.78</x:v>
       </x:c>
       <x:c r="C22" s="7" t="n">
-        <x:v>1.83</x:v>
+        <x:v>1.7500000000000002</x:v>
       </x:c>
       <x:c r="D22" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="E22" s="7" t="n">
-        <x:v>5.01</x:v>
+        <x:v>3.55</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
-        <x:v>Yo-Chi Cronulla</x:v>
+        <x:v>Yo-Chi Currambine</x:v>
       </x:c>
       <x:c r="B23" s="7" t="n">
-        <x:v>24.19</x:v>
+        <x:v>23.799999999999997</x:v>
       </x:c>
       <x:c r="C23" s="7" t="n">
-        <x:v>1.78</x:v>
+        <x:v>1.5699999999999998</x:v>
       </x:c>
       <x:c r="D23" s="7" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
-        <x:v>3.61</x:v>
+        <x:v>6.75</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
-        <x:v>Yo-Chi Currambine</x:v>
+        <x:v>Yo-Chi Double Bay</x:v>
       </x:c>
       <x:c r="B24" s="7" t="n">
-        <x:v>24.16</x:v>
+        <x:v>24.03</x:v>
       </x:c>
       <x:c r="C24" s="7" t="n">
-        <x:v>1.59</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="D24" s="7" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.59</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
-        <x:v>6.8500000000000005</x:v>
+        <x:v>5.3100000000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="7" t="str">
-        <x:v>Yo-Chi Double Bay</x:v>
+        <x:v>Yo-Chi Eastland</x:v>
       </x:c>
       <x:c r="B25" s="7" t="n">
-        <x:v>24.41</x:v>
+        <x:v>23.04</x:v>
       </x:c>
       <x:c r="C25" s="7" t="n">
-        <x:v>2.11</x:v>
+        <x:v>1.69</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
-        <x:v>5.390000000000001</x:v>
+        <x:v>4.760000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="7" t="str">
-        <x:v>Yo-Chi Eastland</x:v>
+        <x:v>Yo-Chi Forrest Chase</x:v>
       </x:c>
       <x:c r="B26" s="7" t="n">
-        <x:v>23.43</x:v>
+        <x:v>24.11</x:v>
       </x:c>
       <x:c r="C26" s="7" t="n">
-        <x:v>1.72</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.35000000000000003</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
-        <x:v>4.84</x:v>
+        <x:v>4.06</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
-        <x:v>Yo-Chi Forrest Chase</x:v>
+        <x:v>Yo-Chi Fremantle</x:v>
       </x:c>
       <x:c r="B27" s="7" t="n">
-        <x:v>24.51</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="C27" s="7" t="n">
-        <x:v>1.7999999999999998</x:v>
+        <x:v>1.5599999999999998</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>4.130000000000001</x:v>
+        <x:v>4.88</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="7" t="str">
-        <x:v>Yo-Chi Fremantle</x:v>
+        <x:v>Yo-Chi Gasworks</x:v>
       </x:c>
       <x:c r="B28" s="7" t="n">
-        <x:v>24.34</x:v>
+        <x:v>25.019999999999996</x:v>
       </x:c>
       <x:c r="C28" s="7" t="n">
-        <x:v>1.59</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="D28" s="7" t="n">
-        <x:v>0.31</x:v>
+        <x:v>0.38999999999999996</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>4.96</x:v>
+        <x:v>4.88</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
-        <x:v>Yo-Chi Gasworks</x:v>
+        <x:v>Yo-Chi George St</x:v>
       </x:c>
       <x:c r="B29" s="7" t="n">
-        <x:v>25.41</x:v>
+        <x:v>23.380000000000003</x:v>
       </x:c>
       <x:c r="C29" s="7" t="n">
-        <x:v>1.83</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="D29" s="7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>4.96</x:v>
+        <x:v>3.85</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="7" t="str">
-        <x:v>Yo-Chi George St</x:v>
+        <x:v>Yo-Chi Glenelg</x:v>
       </x:c>
       <x:c r="B30" s="7" t="n">
-        <x:v>23.78</x:v>
+        <x:v>24.18</x:v>
       </x:c>
       <x:c r="C30" s="7" t="n">
-        <x:v>1.76</x:v>
+        <x:v>1.6099999999999999</x:v>
       </x:c>
       <x:c r="D30" s="7" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>3.92</x:v>
+        <x:v>5.62</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="7" t="str">
-        <x:v>Yo-Chi Glenelg</x:v>
+        <x:v>Yo-Chi Gouger St</x:v>
       </x:c>
       <x:c r="B31" s="7" t="n">
-        <x:v>24.560000000000002</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="C31" s="7" t="n">
-        <x:v>1.6400000000000001</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="D31" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.41000000000000003</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.82</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="7" t="str">
-        <x:v>Yo-Chi Gouger St</x:v>
+        <x:v>Yo-Chi Harbour Town</x:v>
       </x:c>
       <x:c r="B32" s="7" t="n">
-        <x:v>22.89</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="7" t="n">
-        <x:v>1.9800000000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="7" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>5.91</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
-        <x:v>Yo-Chi Harbour Town</x:v>
+        <x:v>Yo-Chi Hawthorn</x:v>
       </x:c>
       <x:c r="B33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>23.580000000000002</x:v>
       </x:c>
       <x:c r="C33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1.9900000000000002</x:v>
       </x:c>
       <x:c r="D33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>6.800000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
-        <x:v>Yo-Chi Hawthorn</x:v>
+        <x:v>Yo-Chi Henley Beach</x:v>
       </x:c>
       <x:c r="B34" s="7" t="n">
-        <x:v>23.94</x:v>
+        <x:v>23.74</x:v>
       </x:c>
       <x:c r="C34" s="7" t="n">
-        <x:v>2.02</x:v>
+        <x:v>1.7500000000000002</x:v>
       </x:c>
       <x:c r="D34" s="7" t="n">
-        <x:v>0.33</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>6.9</x:v>
+        <x:v>5.83</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="7" t="str">
-        <x:v>Yo-Chi Henley Beach</x:v>
+        <x:v>Yo-Chi Highgate</x:v>
       </x:c>
       <x:c r="B35" s="7" t="n">
-        <x:v>24.11</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="C35" s="7" t="n">
-        <x:v>1.78</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="D35" s="7" t="n">
-        <x:v>0.37</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>5.92</x:v>
+        <x:v>6.54</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="str">
-        <x:v>Yo-Chi Highgate</x:v>
+        <x:v>Yo-Chi Highpoint</x:v>
       </x:c>
       <x:c r="B36" s="7" t="n">
-        <x:v>24.060000000000002</x:v>
+        <x:v>22.75</x:v>
       </x:c>
       <x:c r="C36" s="7" t="n">
-        <x:v>2.06</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D36" s="7" t="n">
-        <x:v>0.51</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>6.64</x:v>
+        <x:v>3.84</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
-        <x:v>Yo-Chi Highpoint</x:v>
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
-        <x:v>23.150000000000002</x:v>
+        <x:v>20.13</x:v>
       </x:c>
       <x:c r="C37" s="7" t="n">
-        <x:v>1.7999999999999998</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="D37" s="7" t="n">
-        <x:v>0.22</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>3.91</x:v>
+        <x:v>7.79</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
-        <x:v>Yo-Chi Indooroopilly</x:v>
+        <x:v>Yo-Chi Karrinyup</x:v>
       </x:c>
       <x:c r="B38" s="7" t="n">
-        <x:v>20.47</x:v>
+        <x:v>24.33</x:v>
       </x:c>
       <x:c r="C38" s="7" t="n">
-        <x:v>1.7500000000000002</x:v>
+        <x:v>1.87</x:v>
       </x:c>
       <x:c r="D38" s="7" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="E38" s="7" t="n">
-        <x:v>7.920000000000001</x:v>
+        <x:v>5.57</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="7" t="str">
-        <x:v>Yo-Chi Karrinyup</x:v>
+        <x:v>Yo-Chi Kawana Waters</x:v>
       </x:c>
       <x:c r="B39" s="7" t="n">
-        <x:v>24.709999999999997</x:v>
+        <x:v>15.32</x:v>
       </x:c>
       <x:c r="C39" s="7" t="n">
-        <x:v>1.9</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="D39" s="7" t="n">
-        <x:v>0.53</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E39" s="7" t="n">
-        <x:v>5.66</x:v>
+        <x:v>8.4</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="7" t="str">
-        <x:v>Yo-Chi Kawana Waters</x:v>
+        <x:v>Yo-Chi Lane Cove</x:v>
       </x:c>
       <x:c r="B40" s="7" t="n">
-        <x:v>15.629999999999999</x:v>
+        <x:v>24.01</x:v>
       </x:c>
       <x:c r="C40" s="7" t="n">
-        <x:v>1.34</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="D40" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5599999999999999</x:v>
       </x:c>
       <x:c r="E40" s="7" t="n">
-        <x:v>8.57</x:v>
+        <x:v>6.069999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
-        <x:v>Yo-Chi Lane Cove</x:v>
+        <x:v>Yo-Chi Leederville</x:v>
       </x:c>
       <x:c r="B41" s="7" t="n">
-        <x:v>24.37</x:v>
+        <x:v>24.18</x:v>
       </x:c>
       <x:c r="C41" s="7" t="n">
-        <x:v>2.3800000000000003</x:v>
+        <x:v>1.7000000000000002</x:v>
       </x:c>
       <x:c r="D41" s="7" t="n">
-        <x:v>0.5700000000000001</x:v>
+        <x:v>0.44999999999999996</x:v>
       </x:c>
       <x:c r="E41" s="7" t="n">
-        <x:v>6.16</x:v>
+        <x:v>6.11</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="7" t="str">
-        <x:v>Yo-Chi Leederville</x:v>
+        <x:v>Yo-Chi Macquarie</x:v>
       </x:c>
       <x:c r="B42" s="7" t="n">
-        <x:v>24.55</x:v>
+        <x:v>24.11</x:v>
       </x:c>
       <x:c r="C42" s="7" t="n">
-        <x:v>1.73</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="D42" s="7" t="n">
-        <x:v>0.45999999999999996</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="E42" s="7" t="n">
-        <x:v>6.2</x:v>
+        <x:v>4.95</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
-        <x:v>Yo-Chi Macquarie</x:v>
+        <x:v>Yo-Chi Malvern</x:v>
       </x:c>
       <x:c r="B43" s="7" t="n">
-        <x:v>24.490000000000002</x:v>
+        <x:v>23.45</x:v>
       </x:c>
       <x:c r="C43" s="7" t="n">
-        <x:v>2.15</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="D43" s="7" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E43" s="7" t="n">
-        <x:v>5.029999999999999</x:v>
+        <x:v>6.83</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="str">
-        <x:v>Yo-Chi Malvern</x:v>
+        <x:v>Yo-Chi Mandurah</x:v>
       </x:c>
       <x:c r="B44" s="7" t="n">
-        <x:v>23.810000000000002</x:v>
+        <x:v>23.3</x:v>
       </x:c>
       <x:c r="C44" s="7" t="n">
-        <x:v>1.9800000000000002</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
-        <x:v>0.51</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="E44" s="7" t="n">
-        <x:v>6.93</x:v>
+        <x:v>4.92</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
-        <x:v>Yo-Chi Mandurah</x:v>
+        <x:v>Yo-Chi Manly</x:v>
       </x:c>
       <x:c r="B45" s="7" t="n">
-        <x:v>23.69</x:v>
+        <x:v>24.94</x:v>
       </x:c>
       <x:c r="C45" s="7" t="n">
-        <x:v>1.52</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>0.38999999999999996</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>3.93</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="str">
-        <x:v>Yo-Chi Manly</x:v>
+        <x:v>Yo-Chi Mt Gravatt</x:v>
       </x:c>
       <x:c r="B46" s="7" t="n">
-        <x:v>25.35</x:v>
+        <x:v>23.189999999999998</x:v>
       </x:c>
       <x:c r="C46" s="7" t="n">
-        <x:v>1.71</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="D46" s="7" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>3.9899999999999998</x:v>
+        <x:v>4.82</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
-        <x:v>Yo-Chi Mt Gravatt</x:v>
+        <x:v>Yo-Chi Newtown</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
-        <x:v>23.57</x:v>
+        <x:v>24.22</x:v>
       </x:c>
       <x:c r="C47" s="7" t="n">
-        <x:v>1.9800000000000002</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D47" s="7" t="n">
-        <x:v>0.22</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>4.9</x:v>
+        <x:v>4.81</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="str">
-        <x:v>Yo-Chi Newtown</x:v>
+        <x:v>Yo-Chi Noosa</x:v>
       </x:c>
       <x:c r="B48" s="7" t="n">
-        <x:v>24.6</x:v>
+        <x:v>26.13</x:v>
       </x:c>
       <x:c r="C48" s="7" t="n">
-        <x:v>2.03</x:v>
+        <x:v>1.6199999999999999</x:v>
       </x:c>
       <x:c r="D48" s="7" t="n">
-        <x:v>0.44999999999999996</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>4.89</x:v>
+        <x:v>3.49</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
-        <x:v>Yo-Chi Noosa</x:v>
+        <x:v>Yo-Chi Norwood</x:v>
       </x:c>
       <x:c r="B49" s="7" t="n">
-        <x:v>26.55</x:v>
+        <x:v>24.91</x:v>
       </x:c>
       <x:c r="C49" s="7" t="n">
-        <x:v>1.6500000000000001</x:v>
+        <x:v>1.9300000000000002</x:v>
       </x:c>
       <x:c r="D49" s="7" t="n">
-        <x:v>0.22</x:v>
+        <x:v>0.47000000000000003</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>3.55</x:v>
+        <x:v>5.8500000000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="str">
-        <x:v>Yo-Chi Norwood</x:v>
+        <x:v>Yo-Chi Paddington</x:v>
       </x:c>
       <x:c r="B50" s="7" t="n">
-        <x:v>25.290000000000003</x:v>
+        <x:v>26.009999999999998</x:v>
       </x:c>
       <x:c r="C50" s="7" t="n">
-        <x:v>1.96</x:v>
+        <x:v>1.79</x:v>
       </x:c>
       <x:c r="D50" s="7" t="n">
-        <x:v>0.48</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
-        <x:v>5.94</x:v>
+        <x:v>5.8500000000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
-        <x:v>Yo-Chi Paddington</x:v>
+        <x:v>Yo-Chi Penrith</x:v>
       </x:c>
       <x:c r="B51" s="7" t="n">
-        <x:v>26.39</x:v>
+        <x:v>24.2</x:v>
       </x:c>
       <x:c r="C51" s="7" t="n">
-        <x:v>1.82</x:v>
+        <x:v>1.7500000000000002</x:v>
       </x:c>
       <x:c r="D51" s="7" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
-        <x:v>5.94</x:v>
+        <x:v>3.85</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="str">
-        <x:v>Yo-Chi Penrith</x:v>
+        <x:v>Yo-Chi Prospect</x:v>
       </x:c>
       <x:c r="B52" s="7" t="n">
-        <x:v>24.6</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C52" s="7" t="n">
-        <x:v>1.78</x:v>
+        <x:v>1.92</x:v>
       </x:c>
       <x:c r="D52" s="7" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.5599999999999999</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
-        <x:v>3.91</x:v>
+        <x:v>6.260000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="7" t="str">
-        <x:v>Yo-Chi Prospect</x:v>
+        <x:v>Yo-Chi QV</x:v>
       </x:c>
       <x:c r="B53" s="7" t="n">
-        <x:v>24.89</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="C53" s="7" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.6199999999999999</x:v>
       </x:c>
       <x:c r="D53" s="7" t="n">
-        <x:v>0.5700000000000001</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
-        <x:v>6.35</x:v>
+        <x:v>4.46</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="str">
-        <x:v>Yo-Chi QV</x:v>
+        <x:v>Yo-Chi Randwick</x:v>
       </x:c>
       <x:c r="B54" s="7" t="n">
-        <x:v>22.470000000000002</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C54" s="7" t="n">
-        <x:v>1.6500000000000001</x:v>
+        <x:v>1.6099999999999999</x:v>
       </x:c>
       <x:c r="D54" s="7" t="n">
-        <x:v>0.19</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>4.54</x:v>
+        <x:v>6.890000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="str">
-        <x:v>Yo-Chi Randwick</x:v>
+        <x:v>Yo-Chi Robina</x:v>
       </x:c>
       <x:c r="B55" s="7" t="n">
-        <x:v>25.369999999999997</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="C55" s="7" t="n">
-        <x:v>1.63</x:v>
+        <x:v>1.8599999999999999</x:v>
       </x:c>
       <x:c r="D55" s="7" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.35000000000000003</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>6.99</x:v>
+        <x:v>5.680000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7" t="str">
-        <x:v>Yo-Chi Robina</x:v>
+        <x:v>Yo-Chi Rouse Hill</x:v>
       </x:c>
       <x:c r="B56" s="7" t="n">
-        <x:v>24.08</x:v>
+        <x:v>23.419999999999998</x:v>
       </x:c>
       <x:c r="C56" s="7" t="n">
-        <x:v>1.8900000000000001</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D56" s="7" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>5.7700000000000005</x:v>
+        <x:v>4.130000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="str">
-        <x:v>Yo-Chi Rouse Hill</x:v>
+        <x:v>Yo-Chi Semaphore</x:v>
       </x:c>
       <x:c r="B57" s="7" t="n">
-        <x:v>23.82</x:v>
+        <x:v>24.58</x:v>
       </x:c>
       <x:c r="C57" s="7" t="n">
-        <x:v>1.7999999999999998</x:v>
+        <x:v>1.79</x:v>
       </x:c>
       <x:c r="D57" s="7" t="n">
-        <x:v>0.26</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="E57" s="7" t="n">
-        <x:v>4.2</x:v>
+        <x:v>6.54</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="str">
-        <x:v>Yo-Chi Semaphore</x:v>
+        <x:v>Yo-Chi South Perth</x:v>
       </x:c>
       <x:c r="B58" s="7" t="n">
-        <x:v>24.95</x:v>
+        <x:v>24.03</x:v>
       </x:c>
       <x:c r="C58" s="7" t="n">
-        <x:v>1.82</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D58" s="7" t="n">
-        <x:v>0.59</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="E58" s="7" t="n">
-        <x:v>6.64</x:v>
+        <x:v>5.91</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="str">
-        <x:v>Yo-Chi South Perth</x:v>
+        <x:v>Yo-Chi Southbank</x:v>
       </x:c>
       <x:c r="B59" s="7" t="n">
-        <x:v>24.41</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C59" s="7" t="n">
-        <x:v>1.46</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="D59" s="7" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>6.79</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="str">
-        <x:v>Yo-Chi Southbank</x:v>
+        <x:v>Yo-Chi Southland</x:v>
       </x:c>
       <x:c r="B60" s="7" t="n">
-        <x:v>19.35</x:v>
+        <x:v>23.76</x:v>
       </x:c>
       <x:c r="C60" s="7" t="n">
-        <x:v>1.71</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D60" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
-        <x:v>6.909999999999999</x:v>
+        <x:v>4.74</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="str">
-        <x:v>Yo-Chi Southland</x:v>
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
       </x:c>
       <x:c r="B61" s="7" t="n">
-        <x:v>24.15</x:v>
+        <x:v>24.67</x:v>
       </x:c>
       <x:c r="C61" s="7" t="n">
-        <x:v>1.7999999999999998</x:v>
+        <x:v>1.7399999999999998</x:v>
       </x:c>
       <x:c r="D61" s="7" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.16999999999999998</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>4.82</x:v>
+        <x:v>4.45</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="str">
-        <x:v>Yo-Chi Sunshine Plaza</x:v>
+        <x:v>Yo-Chi Surry Hills</x:v>
       </x:c>
       <x:c r="B62" s="7" t="n">
-        <x:v>25.069999999999997</x:v>
+        <x:v>24.54</x:v>
       </x:c>
       <x:c r="C62" s="7" t="n">
-        <x:v>1.77</x:v>
+        <x:v>1.9800000000000002</x:v>
       </x:c>
       <x:c r="D62" s="7" t="n">
-        <x:v>0.16999999999999998</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>4.52</x:v>
+        <x:v>5.3</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="7" t="str">
-        <x:v>Yo-Chi Surry Hills</x:v>
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
       </x:c>
       <x:c r="B63" s="7" t="n">
-        <x:v>24.92</x:v>
+        <x:v>24.03</x:v>
       </x:c>
       <x:c r="C63" s="7" t="n">
-        <x:v>2.01</x:v>
+        <x:v>1.91</x:v>
       </x:c>
       <x:c r="D63" s="7" t="n">
-        <x:v>0.41000000000000003</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="E63" s="7" t="n">
-        <x:v>5.38</x:v>
+        <x:v>5.8999999999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="str">
-        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
       </x:c>
       <x:c r="B64" s="7" t="n">
-        <x:v>24.4</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="C64" s="7" t="n">
-        <x:v>1.94</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="D64" s="7" t="n">
-        <x:v>0.44</x:v>
+        <x:v>0.22999999999999998</x:v>
       </x:c>
       <x:c r="E64" s="7" t="n">
-        <x:v>5.99</x:v>
+        <x:v>2.83</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="str">
-        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+        <x:v>Yo-Chi Top Ryde</x:v>
       </x:c>
       <x:c r="B65" s="7" t="n">
-        <x:v>24.37</x:v>
+        <x:v>23.47</x:v>
       </x:c>
       <x:c r="C65" s="7" t="n">
-        <x:v>1.76</x:v>
+        <x:v>2.07</x:v>
       </x:c>
       <x:c r="D65" s="7" t="n">
-        <x:v>0.22999999999999998</x:v>
+        <x:v>0.41000000000000003</x:v>
       </x:c>
       <x:c r="E65" s="7" t="n">
-        <x:v>2.88</x:v>
+        <x:v>6.17</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="str">
-        <x:v>Yo-Chi Top Ryde</x:v>
+        <x:v>Yo-Chi Vic Park</x:v>
       </x:c>
       <x:c r="B66" s="7" t="n">
-        <x:v>23.84</x:v>
+        <x:v>23.369999999999997</x:v>
       </x:c>
       <x:c r="C66" s="7" t="n">
-        <x:v>2.1</x:v>
+        <x:v>1.81</x:v>
       </x:c>
       <x:c r="D66" s="7" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
-        <x:v>6.2700000000000005</x:v>
+        <x:v>5.54</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="str">
-        <x:v>Yo-Chi Vic Park</x:v>
+        <x:v>Yo-Chi West End</x:v>
       </x:c>
       <x:c r="B67" s="7" t="n">
-        <x:v>23.74</x:v>
+        <x:v>25.380000000000003</x:v>
       </x:c>
       <x:c r="C67" s="7" t="n">
-        <x:v>1.8399999999999999</x:v>
+        <x:v>1.6400000000000001</x:v>
       </x:c>
       <x:c r="D67" s="7" t="n">
-        <x:v>0.44999999999999996</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
-        <x:v>5.63</x:v>
+        <x:v>5.53</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="str">
-        <x:v>Yo-Chi West End</x:v>
+        <x:v>Yo-Chi Whitford City</x:v>
       </x:c>
       <x:c r="B68" s="7" t="n">
-        <x:v>25.77</x:v>
+        <x:v>23.61</x:v>
       </x:c>
       <x:c r="C68" s="7" t="n">
-        <x:v>1.66</x:v>
+        <x:v>1.6400000000000001</x:v>
       </x:c>
       <x:c r="D68" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
-        <x:v>5.609999999999999</x:v>
+        <x:v>7.140000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="str">
-        <x:v>Yo-Chi Whitford City</x:v>
+        <x:v>Yo-Chi Windsor</x:v>
       </x:c>
       <x:c r="B69" s="7" t="n">
-        <x:v>23.97</x:v>
+        <x:v>23.48</x:v>
       </x:c>
       <x:c r="C69" s="7" t="n">
-        <x:v>1.66</x:v>
+        <x:v>1.8800000000000001</x:v>
       </x:c>
       <x:c r="D69" s="7" t="n">
-        <x:v>0.53</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
-        <x:v>7.249999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="7" t="str">
-        <x:v>Yo-Chi Windsor</x:v>
-      </x:c>
-      <x:c r="B70" s="7" t="n">
-        <x:v>23.86</x:v>
-      </x:c>
-      <x:c r="C70" s="7" t="n">
-        <x:v>1.91</x:v>
-      </x:c>
-      <x:c r="D70" s="7" t="n">
-        <x:v>0.44</x:v>
-      </x:c>
-      <x:c r="E70" s="7" t="n">
-        <x:v>5.390000000000001</x:v>
+        <x:v>5.3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
